--- a/AncillaryFiles/N4VDP_Analysis_V3.xlsx
+++ b/AncillaryFiles/N4VDP_Analysis_V3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33951" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34214" uniqueCount="263">
   <si>
     <t>Participant</t>
   </si>
@@ -800,6 +800,9 @@
   <si>
     <t>AHA-010_V1_FirstVG</t>
   </si>
+  <si>
+    <t>Xe-113</t>
+  </si>
 </sst>
 </file>
 
@@ -844,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK226"/>
+  <dimension ref="A1:AK227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="true"/>
@@ -26200,19 +26203,19 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c r="B225" s="0">
-        <v>2.4779129607044053</v>
+        <v>0</v>
       </c>
       <c r="C225" s="0">
-        <v>18.038492429425588</v>
+        <v>1.0872158413142021</v>
       </c>
       <c r="D225" s="0">
-        <v>78.513847160662763</v>
+        <v>98.912784158685795</v>
       </c>
       <c r="E225" s="0">
-        <v>1.0946842371419221</v>
+        <v>0</v>
       </c>
       <c r="F225" s="0">
         <v>0</v>
@@ -26221,52 +26224,52 @@
         <v>0</v>
       </c>
       <c r="H225" s="0">
-        <v>26.49849778385936</v>
+        <v>2.1812480828874268</v>
       </c>
       <c r="I225" s="0">
-        <v>21.43260850165095</v>
+        <v>9.5327357622439592</v>
       </c>
       <c r="J225" s="0">
-        <v>37.638694708034627</v>
+        <v>46.123172352680548</v>
       </c>
       <c r="K225" s="0">
-        <v>10.453044590534551</v>
+        <v>33.747997682423915</v>
       </c>
       <c r="L225" s="0">
-        <v>2.534431983817711</v>
+        <v>6.4346818445179101</v>
       </c>
       <c r="M225" s="0">
-        <v>1.4427224321028052</v>
+        <v>1.9801642752462423</v>
       </c>
       <c r="N225" s="0">
-        <v>21.694380819228368</v>
+        <v>0.30673801165604442</v>
       </c>
       <c r="O225" s="0">
-        <v>4.8725347294523598</v>
+        <v>0.664599025254763</v>
       </c>
       <c r="P225" s="0">
-        <v>69.316119820329007</v>
+        <v>12.889812889812891</v>
       </c>
       <c r="Q225" s="0">
-        <v>4.1139899455632563</v>
+        <v>75.706349476841282</v>
       </c>
       <c r="R225" s="0">
-        <v>0.002974685427016093</v>
+        <v>10.432500596435021</v>
       </c>
       <c r="S225" s="0">
         <v>0</v>
       </c>
       <c r="T225" s="0">
-        <v>25.731028943689203</v>
+        <v>8.312600115878805</v>
       </c>
       <c r="U225" s="0">
-        <v>32.308058422821787</v>
+        <v>41.464162775638187</v>
       </c>
       <c r="V225" s="0">
-        <v>35.794389743284647</v>
+        <v>41.021096758801676</v>
       </c>
       <c r="W225" s="0">
-        <v>6.1665228902043605</v>
+        <v>9.2021403496813328</v>
       </c>
       <c r="X225" s="0">
         <v>0</v>
@@ -26275,34 +26278,34 @@
         <v>0</v>
       </c>
       <c r="Z225" s="0">
-        <v>20.558050986108221</v>
+        <v>4.2636583620190178</v>
       </c>
       <c r="AA225" s="0">
-        <v>11.22943748698575</v>
+        <v>13.097713097713099</v>
       </c>
       <c r="AB225" s="0">
-        <v>27.016093048160155</v>
+        <v>29.07194710473399</v>
       </c>
       <c r="AC225" s="0">
-        <v>28.137549454145223</v>
+        <v>33.5094236733581</v>
       </c>
       <c r="AD225" s="0">
-        <v>10.607728232739388</v>
+        <v>15.09832657373641</v>
       </c>
       <c r="AE225" s="0">
-        <v>2.4511407918612607</v>
+        <v>4.9589311884393856</v>
       </c>
       <c r="AF225" s="0">
-        <v>11.488235119136151</v>
+        <v>0.12610340479192939</v>
       </c>
       <c r="AG225" s="0">
-        <v>23.360204658357379</v>
+        <v>3.1253195187621414</v>
       </c>
       <c r="AH225" s="0">
-        <v>47.856739149834901</v>
+        <v>41.859513990661533</v>
       </c>
       <c r="AI225" s="0">
-        <v>7.4188654549781363</v>
+        <v>47.980641423264373</v>
       </c>
       <c r="AJ225" s="0">
         <v>0</v>
@@ -26313,114 +26316,227 @@
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B226" s="0">
+        <v>2.4779129607044053</v>
+      </c>
+      <c r="C226" s="0">
+        <v>18.038492429425588</v>
+      </c>
+      <c r="D226" s="0">
+        <v>78.513847160662763</v>
+      </c>
+      <c r="E226" s="0">
+        <v>1.0946842371419221</v>
+      </c>
+      <c r="F226" s="0">
+        <v>0</v>
+      </c>
+      <c r="G226" s="0">
+        <v>0</v>
+      </c>
+      <c r="H226" s="0">
+        <v>26.49849778385936</v>
+      </c>
+      <c r="I226" s="0">
+        <v>21.43260850165095</v>
+      </c>
+      <c r="J226" s="0">
+        <v>37.638694708034627</v>
+      </c>
+      <c r="K226" s="0">
+        <v>10.453044590534551</v>
+      </c>
+      <c r="L226" s="0">
+        <v>2.534431983817711</v>
+      </c>
+      <c r="M226" s="0">
+        <v>1.4427224321028052</v>
+      </c>
+      <c r="N226" s="0">
+        <v>21.694380819228368</v>
+      </c>
+      <c r="O226" s="0">
+        <v>4.8725347294523598</v>
+      </c>
+      <c r="P226" s="0">
+        <v>69.316119820329007</v>
+      </c>
+      <c r="Q226" s="0">
+        <v>4.1139899455632563</v>
+      </c>
+      <c r="R226" s="0">
+        <v>0.002974685427016093</v>
+      </c>
+      <c r="S226" s="0">
+        <v>0</v>
+      </c>
+      <c r="T226" s="0">
+        <v>25.731028943689203</v>
+      </c>
+      <c r="U226" s="0">
+        <v>32.308058422821787</v>
+      </c>
+      <c r="V226" s="0">
+        <v>35.794389743284647</v>
+      </c>
+      <c r="W226" s="0">
+        <v>6.1665228902043605</v>
+      </c>
+      <c r="X226" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y226" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z226" s="0">
+        <v>20.558050986108221</v>
+      </c>
+      <c r="AA226" s="0">
+        <v>11.22943748698575</v>
+      </c>
+      <c r="AB226" s="0">
+        <v>27.016093048160155</v>
+      </c>
+      <c r="AC226" s="0">
+        <v>28.137549454145223</v>
+      </c>
+      <c r="AD226" s="0">
+        <v>10.607728232739388</v>
+      </c>
+      <c r="AE226" s="0">
+        <v>2.4511407918612607</v>
+      </c>
+      <c r="AF226" s="0">
+        <v>11.488235119136151</v>
+      </c>
+      <c r="AG226" s="0">
+        <v>23.360204658357379</v>
+      </c>
+      <c r="AH226" s="0">
+        <v>47.856739149834901</v>
+      </c>
+      <c r="AI226" s="0">
+        <v>7.4188654549781363</v>
+      </c>
+      <c r="AJ226" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK226" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="B226" s="0">
+      <c r="B227" s="0">
         <v>0.0047360818394941865</v>
       </c>
-      <c r="C226" s="0">
+      <c r="C227" s="0">
         <v>0.71041227592412792</v>
       </c>
-      <c r="D226" s="0">
+      <c r="D227" s="0">
         <v>99.308532051433858</v>
       </c>
-      <c r="E226" s="0">
-        <v>0</v>
-      </c>
-      <c r="F226" s="0">
-        <v>0</v>
-      </c>
-      <c r="G226" s="0">
-        <v>0</v>
-      </c>
-      <c r="H226" s="0">
+      <c r="E227" s="0">
+        <v>0</v>
+      </c>
+      <c r="F227" s="0">
+        <v>0</v>
+      </c>
+      <c r="G227" s="0">
+        <v>0</v>
+      </c>
+      <c r="H227" s="0">
         <v>2.8937460039309482</v>
       </c>
-      <c r="I226" s="0">
+      <c r="I227" s="0">
         <v>11.662601529754433</v>
       </c>
-      <c r="J226" s="0">
+      <c r="J227" s="0">
         <v>35.044637571337233</v>
       </c>
-      <c r="K226" s="0">
+      <c r="K227" s="0">
         <v>36.79461981103033</v>
       </c>
-      <c r="L226" s="0">
+      <c r="L227" s="0">
         <v>11.42106135594023</v>
       </c>
-      <c r="M226" s="0">
+      <c r="M227" s="0">
         <v>2.1833337280068199</v>
       </c>
-      <c r="N226" s="0">
+      <c r="N227" s="0">
         <v>0.48544838854815409</v>
       </c>
-      <c r="O226" s="0">
+      <c r="O227" s="0">
         <v>1.520282270477634</v>
       </c>
-      <c r="P226" s="0">
+      <c r="P227" s="0">
         <v>38.6535319330318</v>
       </c>
-      <c r="Q226" s="0">
+      <c r="Q227" s="0">
         <v>59.336001326102917</v>
       </c>
-      <c r="R226" s="0">
+      <c r="R227" s="0">
         <v>0.0047360818394941865</v>
       </c>
-      <c r="S226" s="0">
-        <v>0</v>
-      </c>
-      <c r="T226" s="0">
+      <c r="S227" s="0">
+        <v>0</v>
+      </c>
+      <c r="T227" s="0">
         <v>11.039806767860949</v>
       </c>
-      <c r="U226" s="0">
+      <c r="U227" s="0">
         <v>35.750313765421865</v>
       </c>
-      <c r="V226" s="0">
+      <c r="V227" s="0">
         <v>39.472874091264302</v>
       </c>
-      <c r="W226" s="0">
+      <c r="W227" s="0">
         <v>13.737005375452888</v>
       </c>
-      <c r="X226" s="0">
-        <v>0</v>
-      </c>
-      <c r="Y226" s="0">
-        <v>0</v>
-      </c>
-      <c r="Z226" s="0">
+      <c r="X227" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y227" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z227" s="0">
         <v>5.8798456037320328</v>
       </c>
-      <c r="AA226" s="0">
+      <c r="AA227" s="0">
         <v>12.377749887518057</v>
       </c>
-      <c r="AB226" s="0">
+      <c r="AB227" s="0">
         <v>23.678041156551185</v>
       </c>
-      <c r="AC226" s="0">
+      <c r="AC227" s="0">
         <v>30.244618627009874</v>
       </c>
-      <c r="AD226" s="0">
+      <c r="AD227" s="0">
         <v>20.687205474910606</v>
       </c>
-      <c r="AE226" s="0">
+      <c r="AE227" s="0">
         <v>7.1325392502782439</v>
       </c>
-      <c r="AF226" s="0">
+      <c r="AF227" s="0">
         <v>0.26285254209192732</v>
       </c>
-      <c r="AG226" s="0">
+      <c r="AG227" s="0">
         <v>6.7323403348409858</v>
       </c>
-      <c r="AH226" s="0">
+      <c r="AH227" s="0">
         <v>46.550948400388357</v>
       </c>
-      <c r="AI226" s="0">
+      <c r="AI227" s="0">
         <v>39.157924648937936</v>
       </c>
-      <c r="AJ226" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK226" s="0">
+      <c r="AJ227" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK227" s="0">
         <v>0</v>
       </c>
     </row>
